--- a/results/ARI.xlsx
+++ b/results/ARI.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JupyterProjects\sect修订中2\result\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JupyterProjects\sect修订中2\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B42654A-3C6F-4D17-9C5C-4E687193907A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB05BEB-38DF-4985-AF6E-1CAD440E529A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="210" yWindow="100" windowWidth="18990" windowHeight="10240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,9 +34,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>g22</t>
-  </si>
-  <si>
     <t>email-Eu-core</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -75,6 +72,10 @@
   </si>
   <si>
     <t>louvain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LFR_base</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -462,7 +463,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -471,21 +472,21 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2">
         <v>2.7650000000000001E-2</v>
@@ -494,10 +495,10 @@
         <v>0.95250000000000001</v>
       </c>
       <c r="D2" s="3">
-        <v>0.63706799999999997</v>
+        <v>0.99254399999999998</v>
       </c>
       <c r="E2" s="2">
-        <v>0.55510000000000004</v>
+        <v>0.56660999999999995</v>
       </c>
       <c r="F2" s="2">
         <v>0.43643599999999999</v>
@@ -508,7 +509,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1">
         <v>1.5176E-2</v>
@@ -517,10 +518,10 @@
         <v>0.73067800000000005</v>
       </c>
       <c r="D3" s="1">
-        <v>0.43002299999999999</v>
+        <v>0.99220699999999995</v>
       </c>
       <c r="E3" s="1">
-        <v>0.26881500000000003</v>
+        <v>0.26127899999999998</v>
       </c>
       <c r="F3" s="1">
         <v>0.39646900000000002</v>
@@ -531,7 +532,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1">
         <v>1.9344E-2</v>
@@ -540,10 +541,10 @@
         <v>0.32175300000000001</v>
       </c>
       <c r="D4" s="1">
-        <v>0.373444</v>
+        <v>1.6063999999999998E-2</v>
       </c>
       <c r="E4" s="1">
-        <v>5.9319999999999998E-3</v>
+        <v>6.6569999999999997E-3</v>
       </c>
       <c r="F4" s="1">
         <v>5.1177E-2</v>
@@ -554,7 +555,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1">
         <v>1.1063999999999999E-2</v>
@@ -563,10 +564,10 @@
         <v>0.73067800000000005</v>
       </c>
       <c r="D5" s="1">
-        <v>0.43002299999999999</v>
+        <v>0.99185999999999996</v>
       </c>
       <c r="E5" s="1">
-        <v>0.25012800000000002</v>
+        <v>0.28200500000000001</v>
       </c>
       <c r="F5" s="1">
         <v>0.39679399999999998</v>
@@ -577,7 +578,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1">
         <v>9.3410000000000003E-3</v>
@@ -586,10 +587,10 @@
         <v>0.90054699999999999</v>
       </c>
       <c r="D6" s="1">
-        <v>0.58692100000000003</v>
+        <v>0.89830900000000002</v>
       </c>
       <c r="E6" s="1">
-        <v>3.6200000000000002E-4</v>
+        <v>8.064E-3</v>
       </c>
       <c r="F6" s="1">
         <v>0.419989</v>
@@ -600,7 +601,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1">
         <v>1.5552E-2</v>
@@ -609,10 +610,10 @@
         <v>0.52640600000000004</v>
       </c>
       <c r="D7" s="1">
-        <v>0.42863299999999999</v>
+        <v>0.94952300000000001</v>
       </c>
       <c r="E7" s="1">
-        <v>0.17230100000000001</v>
+        <v>0.151952</v>
       </c>
       <c r="F7" s="1">
         <v>0.32840900000000001</v>
@@ -623,7 +624,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1">
         <v>5.0509999999999999E-3</v>
@@ -632,10 +633,10 @@
         <v>0.52640600000000004</v>
       </c>
       <c r="D8" s="1">
-        <v>0.62578599999999995</v>
+        <v>0.99185999999999996</v>
       </c>
       <c r="E8" s="1">
-        <v>0.237926</v>
+        <v>0.23693</v>
       </c>
       <c r="F8" s="1">
         <v>0.433917</v>
